--- a/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:59:21+00:00</t>
+    <t>2026-09-11T08:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:08:26+00:00</t>
+    <t>2026-09-11T08:18:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/feat/crmi-artefakt-metadaten/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:18:01+00:00</t>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>Publisher</t>
